--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/oct-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/oct-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1010,7 +1010,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1134432-689-CM26</t>
+          <t>1200-241-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1035,27 +1035,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>8.148.859-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2881.72</v>
+        <v>35338.24</v>
       </c>
     </row>
     <row r="11">
@@ -1132,7 +1132,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1200-241-CM26</t>
+          <t>1134432-689-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1157,27 +1157,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1187,13 +1187,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>35338.24</v>
+        <v>2881.72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1109692-267-CM26</t>
+          <t>1417966-85-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1218,47 +1218,43 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>65.063.166-8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>CORPORACIÓN DESARROLLA BIOBÍO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ALIMENTOS SOL DE QUILLOTA SPA</t>
+          <t>CAROLYN MARLEN</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.850.715-3</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.905.851-6</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1347.14</v>
+        <v>20329.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1417966-85-CM26</t>
+          <t>1109692-267-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1283,37 +1279,41 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>65.063.166-8</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CORPORACIÓN DESARROLLA BIOBÍO</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CAROLYN MARLEN</t>
+          <t>ALIMENTOS SOL DE QUILLOTA SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.905.851-6</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>77.850.715-3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>20329.64</v>
+        <v>1347.14</v>
       </c>
     </row>
     <row r="15">
@@ -1689,7 +1689,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3249-148-CM26</t>
+          <t>2123-369-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.102.049-k</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1744,13 +1744,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2421.8</v>
+        <v>1737.16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4291-1666-CM26</t>
+          <t>3249-148-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1775,47 +1775,43 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.102.049-k</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ALIMENTOS SOL DE QUILLOTA SPA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.850.715-3</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>15327.86</v>
+        <v>2421.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2123-369-CM26</t>
+          <t>4291-1666-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1840,43 +1836,47 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ALIMENTOS SOL DE QUILLOTA SPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77.850.715-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>AUTOMOTRIZ R Y R LIMITADA</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>77.951.690-3</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1737.16</v>
+        <v>15327.86</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1200-252-CM26</t>
+          <t>1134432-704-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1901,47 +1901,43 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALEMOSO SPA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.852.175-K</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>8299.43</v>
+        <v>224.31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1059109-109-CM26</t>
+          <t>4650-148-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1966,27 +1962,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1996,13 +1992,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>44861.8</v>
+        <v>254.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2467-1321-CM26</t>
+          <t>1200-252-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2027,43 +2023,47 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Roberto</t>
+          <t>ALEMOSO SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>77.852.175-K</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>295.68</v>
+        <v>8299.43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4650-148-CM26</t>
+          <t>1059109-109-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2088,27 +2088,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Marcelo Fabian</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2118,13 +2118,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>254.9</v>
+        <v>44861.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1134432-704-CM26</t>
+          <t>2467-1321-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2149,27 +2149,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>224.31</v>
+        <v>295.68</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1457776-43-SE26</t>
+          <t>1777-96-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2210,47 +2210,43 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>60.804.012-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.820.816-6</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>51670.16</v>
+        <v>211983.43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1777-96-CM26</t>
+          <t>2416-270-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2275,12 +2271,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.804.012-9</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2290,12 +2286,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t>CAROLYN MARLEN</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>76.905.851-6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2305,13 +2301,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>211983.43</v>
+        <v>1985.76</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2416-270-CM26</t>
+          <t>5782-45-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2336,27 +2332,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CAROLYN MARLEN</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.905.851-6</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2366,13 +2362,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1985.76</v>
+        <v>455.91</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5782-45-CM26</t>
+          <t>1457776-43-SE26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2397,12 +2393,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2412,22 +2408,26 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>455.91</v>
+        <v>51670.16</v>
       </c>
     </row>
     <row r="33">
@@ -2555,7 +2555,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5952-178-CM26</t>
+          <t>934-198-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2580,27 +2580,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ALEJANDRO RAMÓN GONZÁLEZ SILVA</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>7.115.014-3</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2610,13 +2610,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>305.61</v>
+        <v>3565.43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5952-179-CM26</t>
+          <t>2547-249-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2641,27 +2641,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ALEJANDRO RAMÓN GONZÁLEZ SILVA</t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>7.115.014-3</t>
+          <t>8.148.859-2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2671,13 +2671,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>203.74</v>
+        <v>6825.24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2547-249-CM26</t>
+          <t>5952-178-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2702,27 +2702,27 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t>ALEJANDRO RAMÓN GONZÁLEZ SILVA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
+          <t>7.115.014-3</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2732,13 +2732,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>6825.24</v>
+        <v>305.61</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>934-198-CM26</t>
+          <t>5952-179-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2763,27 +2763,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>ALEJANDRO RAMÓN GONZÁLEZ SILVA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>7.115.014-3</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2793,13 +2793,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3565.43</v>
+        <v>203.74</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5782-48-CM26</t>
+          <t>1300-361-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>61.961.000-8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2854,13 +2854,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>813.4400000000001</v>
+        <v>1527.71</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2546-979-CM26</t>
+          <t>5782-48-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2885,27 +2885,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2915,13 +2915,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>12284.76</v>
+        <v>813.4400000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2292-7344-CM26</t>
+          <t>1134432-720-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2946,47 +2946,43 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>11670.52</v>
+        <v>510.95</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1274188-749-CM26</t>
+          <t>2546-979-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3011,27 +3007,27 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>70.934.900-7</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO SOCIAL DE BUIN</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>8.148.859-2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3041,13 +3037,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>30711.9</v>
+        <v>12284.76</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1057417-17061-SE26</t>
+          <t>2292-7344-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3062,7 +3058,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3072,32 +3068,32 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3106,13 +3102,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>314520.87</v>
+        <v>11670.52</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1057539-8780-CM26</t>
+          <t>1274188-749-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3127,7 +3123,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3137,27 +3133,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>70.934.900-7</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>CORPORACION DE DESARROLLO SOCIAL DE BUIN</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Javier Orlando</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.548.886-9</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3167,67 +3163,193 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>58788.95</v>
+        <v>30711.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>1057417-17061-SE26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.701.245-4</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>314520.87</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1057539-8780-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Javier Orlando</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76.548.886-9</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>58788.95</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>1943-401-CM26</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2239-12-LR25</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>oct-2026</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>61.313.000-4</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">Felipe </t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>76.834.013-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="n">
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
         <v>12163.23</v>
       </c>
     </row>
